--- a/output/pdf_financials_xlsx/EAM.xlsx
+++ b/output/pdf_financials_xlsx/EAM.xlsx
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1721,19 +1721,19 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>88.760025</v>
+        <v>-88.760025</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>109.049125</v>
+        <v>-109.049125</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>108.39636</v>
+        <v>-108.39636</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>156.32475</v>
+        <v>-156.32475</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>163.891825</v>
+        <v>-163.891825</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1887,19 +1887,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2015,19 +2015,19 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -4967,16 +4967,16 @@
         <v>150.368161</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>151.319106</v>
+        <v>151.410259</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>151.410259</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>152.394897</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>152.845956</v>
       </c>
     </row>
     <row r="93">
@@ -8353,7 +8353,11 @@
           <t>Reserves (note 10(e))</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -35966,10 +35970,10 @@
         </is>
       </c>
       <c r="J368" s="5" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="K368" s="5" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -36261,19 +36265,19 @@
         </is>
       </c>
       <c r="G372" s="5" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="H372" s="5" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="I372" s="5" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="J372" s="5" t="n">
-        <v>9.379485000000001</v>
+        <v>-9.379485000000001</v>
       </c>
       <c r="K372" s="5" t="n">
-        <v>6.555673</v>
+        <v>-6.555673</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -36488,19 +36492,19 @@
         </is>
       </c>
       <c r="G375" s="5" t="n">
-        <v>9.187613000000001</v>
+        <v>-9.187613000000001</v>
       </c>
       <c r="H375" s="5" t="n">
-        <v>4.575706</v>
+        <v>-4.575706</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>6.158898</v>
+        <v>-6.158898</v>
       </c>
       <c r="J375" s="5" t="n">
-        <v>10.948455</v>
+        <v>-10.948455</v>
       </c>
       <c r="K375" s="5" t="n">
-        <v>4.675905</v>
+        <v>-4.675905</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -37123,10 +37127,10 @@
         </is>
       </c>
       <c r="H383" s="5" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>5.419818</v>
+        <v>-5.419818</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -38240,10 +38244,10 @@
         </is>
       </c>
       <c r="G397" s="5" t="n">
-        <v>10.651203</v>
+        <v>-10.651203</v>
       </c>
       <c r="H397" s="5" t="n">
-        <v>8.723929999999999</v>
+        <v>-8.723929999999999</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EAM.xlsx
+++ b/output/pdf_financials_xlsx/EAM.xlsx
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.904435</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.190916</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0292</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000553</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.01969</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-10.651203</v>
+        <v>-10.460287</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.723929999999999</v>
+        <v>-8.69473</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.419818</v>
+        <v>-5.419265</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-9.379485000000001</v>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.651203</v>
+        <v>-10.460287</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.723929999999999</v>
+        <v>-8.69473</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.419818</v>
+        <v>-5.419265</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-9.379485000000001</v>
@@ -2170,13 +2170,13 @@
         <v>2.2346</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.347285</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.07686999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.287528</v>
       </c>
     </row>
     <row r="35">
@@ -2262,13 +2262,13 @@
         <v>2.2346</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.347285</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.07686999999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.287528</v>
       </c>
     </row>
     <row r="37">
@@ -2834,13 +2834,13 @@
         <v>5.316468</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.325452</v>
+        <v>4.978167</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.670806</v>
+        <v>4.593936</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.045678</v>
+        <v>4.75815</v>
       </c>
     </row>
     <row r="49">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -32433,7 +32433,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -34971,7 +34971,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -35858,7 +35858,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -37025,7 +37025,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -38147,7 +38147,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -39751,7 +39751,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -42339,7 +42339,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">

--- a/output/pdf_financials_xlsx/EAM.xlsx
+++ b/output/pdf_financials_xlsx/EAM.xlsx
@@ -802,40 +802,40 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.652389</v>
+        <v>1.866112</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.421353</v>
+        <v>0.654195</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.391771</v>
+        <v>0.533451</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.23476</v>
+        <v>0.385491</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.30312</v>
+        <v>0.572945</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.304184</v>
+        <v>0.5611350000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.140781</v>
+        <v>0.223199</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.017541</v>
+        <v>0.048296</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.011034</v>
+        <v>0.012099</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.001561</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>0.001199</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>0.001237</v>
       </c>
     </row>
     <row r="10">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.540805</v>
+        <v>2.754528</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.934684</v>
+        <v>1.167526</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>9.257802</v>
@@ -868,10 +868,10 @@
         <v>6.409313</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.358011</v>
+        <v>0.440429</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.216152</v>
+        <v>0.246907</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>3.036815</v>
@@ -883,7 +883,7 @@
         <v>2.999713</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.253764</v>
+        <v>0.255001</v>
       </c>
     </row>
     <row r="11">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.934684</v>
+        <v>-1.167526</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-9.257802</v>
@@ -32058,7 +32058,11 @@
           <t>Rent and occupancy costs</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -37663,7 +37667,11 @@
           <t>Rent and occupancy costs</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -39188,7 +39196,11 @@
           <t>Rent and occupancy costs 232,842</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -41762,7 +41774,11 @@
           <t>Rent and occupancy costs 113,768</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
